--- a/data/trans_camb/IP16B02-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16B02-Habitat-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,38; 61,05</t>
+          <t>2,29; 62,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,57; 52,34</t>
+          <t>-20,06; 51,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-21,45; 18,5</t>
+          <t>-21,15; 17,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-31,66; 15,66</t>
+          <t>-33,7; 15,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 35,87</t>
+          <t>-4,02; 36,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-17,44; 28,36</t>
+          <t>-18,15; 29,96</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,79; 230,21</t>
+          <t>2,82; 210,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-29,27; 165,66</t>
+          <t>-26,55; 166,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-23,72; 23,82</t>
+          <t>-21,24; 22,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-32,14; 18,49</t>
+          <t>-37,08; 18,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 64,61</t>
+          <t>-4,17; 67,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-20,89; 46,15</t>
+          <t>-21,95; 51,05</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-31,38; 8,28</t>
+          <t>-30,7; 11,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-15,59; 24,25</t>
+          <t>-17,5; 23,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 17,1</t>
+          <t>-11,28; 17,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-20,07; 13,79</t>
+          <t>-17,13; 16,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-18,49; 7,7</t>
+          <t>-17,8; 7,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,2; 12,77</t>
+          <t>-12,91; 11,47</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-32,97; 10,73</t>
+          <t>-33,11; 14,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-16,54; 34,78</t>
+          <t>-17,98; 31,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,58; 21,89</t>
+          <t>-11,68; 21,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-20,77; 17,06</t>
+          <t>-18,06; 20,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-19,84; 9,11</t>
+          <t>-19,34; 9,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-13,25; 15,96</t>
+          <t>-13,81; 14,11</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-29,37; 4,59</t>
+          <t>-28,68; 4,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-35,77; 3,61</t>
+          <t>-36,81; 2,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-18,67; 19,44</t>
+          <t>-20,58; 21,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 25,41</t>
+          <t>-10,23; 26,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-18,62; 10,63</t>
+          <t>-18,78; 9,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,46; 12,57</t>
+          <t>-17,01; 13,69</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-29,65; 5,33</t>
+          <t>-29,85; 4,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-37,08; 1,96</t>
+          <t>-38,51; 1,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-20,17; 28,09</t>
+          <t>-21,99; 31,16</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-11,05; 36,53</t>
+          <t>-10,87; 38,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-19,45; 13,79</t>
+          <t>-20,16; 12,03</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-17,77; 15,64</t>
+          <t>-18,14; 17,72</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-23,95; 22,62</t>
+          <t>-23,21; 22,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-15,74; 28,13</t>
+          <t>-15,77; 27,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-20,75; 14,14</t>
+          <t>-22,15; 13,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,38; 18,26</t>
+          <t>-13,44; 18,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-16,9; 11,45</t>
+          <t>-17,36; 11,85</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,56; 17,73</t>
+          <t>-11,42; 15,76</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-25,11; 33,48</t>
+          <t>-24,6; 31,48</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-16,09; 42,4</t>
+          <t>-15,75; 45,87</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-23,04; 17,75</t>
+          <t>-23,98; 15,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-13,02; 22,58</t>
+          <t>-14,15; 22,2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-17,78; 14,24</t>
+          <t>-18,68; 14,16</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-11,09; 22,43</t>
+          <t>-11,69; 20,18</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-11,16; 13,85</t>
+          <t>-10,37; 14,61</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-11,05; 15,17</t>
+          <t>-9,19; 15,33</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,7; 8,45</t>
+          <t>-10,59; 8,02</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 11,43</t>
+          <t>-6,62; 11,3</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 6,78</t>
+          <t>-8,88; 6,55</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 9,32</t>
+          <t>-6,65; 8,3</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-12,88; 19,7</t>
+          <t>-11,89; 21,32</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-12,64; 21,35</t>
+          <t>-10,72; 21,07</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-11,59; 9,86</t>
+          <t>-11,32; 9,73</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 13,8</t>
+          <t>-7,05; 13,79</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-10,1; 8,24</t>
+          <t>-9,8; 8,24</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 11,44</t>
+          <t>-7,56; 10,25</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16B02-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16B02-Habitat-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,29; 62,76</t>
+          <t>1,74; 61,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-20,06; 51,09</t>
+          <t>-15,87; 50,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-21,15; 17,48</t>
+          <t>-21,71; 15,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-33,7; 15,59</t>
+          <t>-31,48; 15,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 36,39</t>
+          <t>-3,34; 35,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-18,15; 29,96</t>
+          <t>-19,6; 28,25</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,82; 210,02</t>
+          <t>2,77; 206,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-26,55; 166,29</t>
+          <t>-23,71; 164,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-21,24; 22,72</t>
+          <t>-23,68; 19,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-37,08; 18,39</t>
+          <t>-31,79; 18,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 67,74</t>
+          <t>-4,09; 64,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-21,95; 51,05</t>
+          <t>-24,14; 49,9</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-30,7; 11,07</t>
+          <t>-30,84; 10,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-17,5; 23,91</t>
+          <t>-18,83; 23,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,28; 17,07</t>
+          <t>-14,07; 17,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-17,13; 16,35</t>
+          <t>-17,46; 14,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-17,8; 7,95</t>
+          <t>-18,11; 8,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,91; 11,47</t>
+          <t>-12,55; 12,09</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-33,11; 14,39</t>
+          <t>-32,86; 12,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-17,98; 31,89</t>
+          <t>-18,89; 31,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,68; 21,75</t>
+          <t>-12,63; 22,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-18,06; 20,32</t>
+          <t>-18,82; 17,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-19,34; 9,11</t>
+          <t>-19,59; 10,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-13,81; 14,11</t>
+          <t>-13,85; 14,82</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-28,68; 4,75</t>
+          <t>-28,88; 6,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-36,81; 2,16</t>
+          <t>-37,52; 4,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-20,58; 21,03</t>
+          <t>-21,64; 19,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,23; 26,19</t>
+          <t>-12,2; 27,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-18,78; 9,9</t>
+          <t>-17,64; 10,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-17,01; 13,69</t>
+          <t>-16,52; 13,35</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-29,85; 4,6</t>
+          <t>-29,85; 6,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-38,51; 1,34</t>
+          <t>-38,92; 2,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-21,99; 31,16</t>
+          <t>-23,34; 26,91</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-10,87; 38,98</t>
+          <t>-13,3; 39,81</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-20,16; 12,03</t>
+          <t>-19,08; 12,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-18,14; 17,72</t>
+          <t>-17,43; 16,81</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-23,21; 22,42</t>
+          <t>-24,87; 24,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-15,77; 27,32</t>
+          <t>-14,46; 30,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-22,15; 13,57</t>
+          <t>-23,56; 13,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-13,44; 18,15</t>
+          <t>-13,16; 18,18</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-17,36; 11,85</t>
+          <t>-16,78; 11,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,42; 15,76</t>
+          <t>-11,66; 16,76</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-24,6; 31,48</t>
+          <t>-27,22; 35,64</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-15,75; 45,87</t>
+          <t>-15,21; 51,76</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-23,98; 15,97</t>
+          <t>-25,04; 16,56</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-14,15; 22,2</t>
+          <t>-13,89; 22,24</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-18,68; 14,16</t>
+          <t>-17,86; 15,24</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-11,69; 20,18</t>
+          <t>-12,41; 21,34</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 14,61</t>
+          <t>-10,93; 14,12</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-9,19; 15,33</t>
+          <t>-9,26; 15,93</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 8,02</t>
+          <t>-9,97; 8,22</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 11,3</t>
+          <t>-7,17; 10,94</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,88; 6,55</t>
+          <t>-8,29; 5,95</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 8,3</t>
+          <t>-5,57; 8,88</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-11,89; 21,32</t>
+          <t>-12,71; 19,88</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-10,72; 21,07</t>
+          <t>-10,58; 22,07</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-11,32; 9,73</t>
+          <t>-10,94; 9,68</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 13,79</t>
+          <t>-7,7; 13,1</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-9,8; 8,24</t>
+          <t>-9,23; 7,29</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 10,25</t>
+          <t>-6,24; 10,92</t>
         </is>
       </c>
     </row>
